--- a/data/data-wrangling-intermediate/21_treatment-info/model41-treatment-info.xlsx
+++ b/data/data-wrangling-intermediate/21_treatment-info/model41-treatment-info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eltnmsu-my.sharepoint.com/personal/lossanna_nmsu_edu/Documents/Documents/04_LDC-LTDL/LDC-LTDL_v04/data/data-wrangling-intermediate/21_treatment-info/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{F3DA1B3D-C87D-4227-9AB8-F63E6F7EF9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B267A3F5-7C48-4C81-816D-EF6425335B6D}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{F3DA1B3D-C87D-4227-9AB8-F63E6F7EF9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33250817-EC99-40B8-9AD6-DC5BF019B431}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8B3D6DA8-F5BC-487F-8B98-E9951C31C6EA}"/>
+    <workbookView minimized="1" xWindow="7224" yWindow="3792" windowWidth="17208" windowHeight="9888" xr2:uid="{8B3D6DA8-F5BC-487F-8B98-E9951C31C6EA}"/>
   </bookViews>
   <sheets>
     <sheet name="model41-treatment-info" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="231">
   <si>
     <t>Model</t>
   </si>
@@ -704,6 +704,15 @@
   </si>
   <si>
     <t>Targeted creosote</t>
+  </si>
+  <si>
+    <t>Targeted mesquite (tebuthiuron)</t>
+  </si>
+  <si>
+    <t>Brush control (triclopyr and clopyralid)</t>
+  </si>
+  <si>
+    <t>Targeted mesquite (triclopyr and clopyralid)</t>
   </si>
 </sst>
 </file>
@@ -1854,7 +1863,7 @@
         <v>45</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E3" s="1">
         <v>318</v>
@@ -2493,7 +2502,7 @@
         <v>2.4277777777777776</v>
       </c>
     </row>
-    <row r="9" spans="1:44" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:44" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>43</v>
       </c>
@@ -2504,7 +2513,7 @@
         <v>45</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E9" s="1">
         <v>3738</v>
@@ -2610,7 +2619,7 @@
         <v>45</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>155</v>
+        <v>229</v>
       </c>
       <c r="E10" s="1">
         <v>5010</v>
@@ -2716,7 +2725,7 @@
         <v>45</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>155</v>
+        <v>229</v>
       </c>
       <c r="E11" s="1">
         <v>5159</v>
@@ -3250,7 +3259,7 @@
         <v>45</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E16" s="1">
         <v>15329</v>
@@ -3356,7 +3365,7 @@
         <v>45</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E17" s="1">
         <v>15330</v>
@@ -3462,7 +3471,7 @@
         <v>45</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>155</v>
+        <v>226</v>
       </c>
       <c r="E18" s="1">
         <v>17019</v>
@@ -3771,7 +3780,7 @@
         <v>2.3881944444444443</v>
       </c>
     </row>
-    <row r="21" spans="1:44" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:44" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>43</v>
       </c>
@@ -3782,7 +3791,7 @@
         <v>45</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>155</v>
+        <v>229</v>
       </c>
       <c r="E21" s="1">
         <v>19995</v>
@@ -4002,7 +4011,7 @@
         <v>45</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>155</v>
+        <v>229</v>
       </c>
       <c r="E23" s="1">
         <v>23200</v>
@@ -4108,7 +4117,7 @@
         <v>45</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E24" s="1">
         <v>23655</v>
@@ -4532,7 +4541,7 @@
         <v>45</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E28" s="1">
         <v>26019</v>
